--- a/tests/fixtures/amex_activity_sanitized.xlsx
+++ b/tests/fixtures/amex_activity_sanitized.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>320260070187470819</t>
+          <t>REF-20260106-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>320260050078449011</t>
+          <t>REF-20260105-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>320260040078923435</t>
+          <t>REF-20260104-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
